--- a/data/simulated_files/payroll_q1_xlsx.xlsx
+++ b/data/simulated_files/payroll_q1_xlsx.xlsx
@@ -454,10 +454,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -475,10 +473,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23210</v>
+        <v>21154</v>
       </c>
       <c r="F2" t="n">
-        <v>16711</v>
+        <v>15230</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -487,10 +485,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -508,10 +504,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23231</v>
+        <v>24463</v>
       </c>
       <c r="F3" t="n">
-        <v>16726</v>
+        <v>17613</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -520,10 +516,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -541,10 +535,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21360</v>
+        <v>23885</v>
       </c>
       <c r="F4" t="n">
-        <v>15379</v>
+        <v>17197</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -553,10 +547,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -574,10 +566,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24208</v>
+        <v>22193</v>
       </c>
       <c r="F5" t="n">
-        <v>17429</v>
+        <v>15978</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -586,10 +578,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>C005</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -607,10 +597,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25534</v>
+        <v>21786</v>
       </c>
       <c r="F6" t="n">
-        <v>18384</v>
+        <v>15685</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/data/simulated_files/payroll_q1_xlsx.xlsx
+++ b/data/simulated_files/payroll_q1_xlsx.xlsx
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21154</v>
+        <v>21713</v>
       </c>
       <c r="F2" t="n">
-        <v>15230</v>
+        <v>15633</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>24463</v>
+        <v>24447</v>
       </c>
       <c r="F3" t="n">
-        <v>17613</v>
+        <v>17601</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>23885</v>
+        <v>22751</v>
       </c>
       <c r="F4" t="n">
-        <v>17197</v>
+        <v>16380</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22193</v>
+        <v>21746</v>
       </c>
       <c r="F5" t="n">
-        <v>15978</v>
+        <v>15657</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21786</v>
+        <v>23306</v>
       </c>
       <c r="F6" t="n">
-        <v>15685</v>
+        <v>16780</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/data/simulated_files/payroll_q1_xlsx.xlsx
+++ b/data/simulated_files/payroll_q1_xlsx.xlsx
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21713</v>
+        <v>21222</v>
       </c>
       <c r="F2" t="n">
-        <v>15633</v>
+        <v>15279</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>24447</v>
+        <v>22174</v>
       </c>
       <c r="F3" t="n">
-        <v>17601</v>
+        <v>15965</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22751</v>
+        <v>25848</v>
       </c>
       <c r="F4" t="n">
-        <v>16380</v>
+        <v>18610</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21746</v>
+        <v>23446</v>
       </c>
       <c r="F5" t="n">
-        <v>15657</v>
+        <v>16881</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23306</v>
+        <v>23290</v>
       </c>
       <c r="F6" t="n">
-        <v>16780</v>
+        <v>16768</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/data/simulated_files/payroll_q1_xlsx.xlsx
+++ b/data/simulated_files/payroll_q1_xlsx.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll Q1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Payroll Q1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21222</v>
+        <v>22798</v>
       </c>
       <c r="F2" t="n">
-        <v>15279</v>
+        <v>16414</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22174</v>
+        <v>21443</v>
       </c>
       <c r="F3" t="n">
-        <v>15965</v>
+        <v>15438</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25848</v>
+        <v>25686</v>
       </c>
       <c r="F4" t="n">
-        <v>18610</v>
+        <v>18493</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23446</v>
+        <v>25985</v>
       </c>
       <c r="F5" t="n">
-        <v>16881</v>
+        <v>18709</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23290</v>
+        <v>22963</v>
       </c>
       <c r="F6" t="n">
-        <v>16768</v>
+        <v>16533</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
